--- a/e2e-screenshots/accessory-reupload-reconcile/downloaded-inventory-report.xlsx
+++ b/e2e-screenshots/accessory-reupload-reconcile/downloaded-inventory-report.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="20">
   <si>
     <t>Stock In Date</t>
   </si>
@@ -57,6 +57,9 @@
     <t>Name</t>
   </si>
   <si>
+    <t>First Added</t>
+  </si>
+  <si>
     <t>Total Added</t>
   </si>
   <si>
@@ -67,6 +70,9 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>2026-08-02</t>
   </si>
 </sst>
 </file>
@@ -585,16 +591,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="3" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>12</v>
       </c>
@@ -608,34 +614,40 @@
         <v>14</v>
       </c>
       <c r="E1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2">
         <v>50</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>3.5</v>
       </c>
-      <c r="F2" t="s">
-        <v>17</v>
+      <c r="G2" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:G1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/e2e-screenshots/accessory-reupload-reconcile/downloaded-inventory-report.xlsx
+++ b/e2e-screenshots/accessory-reupload-reconcile/downloaded-inventory-report.xlsx
@@ -72,7 +72,7 @@
     <t/>
   </si>
   <si>
-    <t>2026-08-02</t>
+    <t>2026-08-07</t>
   </si>
 </sst>
 </file>
